--- a/User_Data/ABS/Full_Sheets/634501.xlsx
+++ b/User_Data/ABS/Full_Sheets/634501.xlsx
@@ -17,89 +17,89 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2603039T">Data1!$B$1:$B$10,Data1!$B$11:$B$123</definedName>
-    <definedName name="A2603039T_Data">Data1!$B$11:$B$123</definedName>
-    <definedName name="A2603039T_Latest">Data1!$B$123</definedName>
-    <definedName name="A2603040A">Data1!$K$1:$K$10,Data1!$K$11:$K$123</definedName>
-    <definedName name="A2603040A_Data">Data1!$K$11:$K$123</definedName>
-    <definedName name="A2603040A_Latest">Data1!$K$123</definedName>
-    <definedName name="A2603041C">Data1!$T$1:$T$10,Data1!$T$11:$T$123</definedName>
-    <definedName name="A2603041C_Data">Data1!$T$11:$T$123</definedName>
-    <definedName name="A2603041C_Latest">Data1!$T$123</definedName>
-    <definedName name="A2603609J">Data1!$D$1:$D$10,Data1!$D$11:$D$123</definedName>
-    <definedName name="A2603609J_Data">Data1!$D$11:$D$123</definedName>
-    <definedName name="A2603609J_Latest">Data1!$D$123</definedName>
-    <definedName name="A2603610T">Data1!$M$1:$M$10,Data1!$M$11:$M$123</definedName>
-    <definedName name="A2603610T_Data">Data1!$M$11:$M$123</definedName>
-    <definedName name="A2603610T_Latest">Data1!$M$123</definedName>
-    <definedName name="A2603611V">Data1!$V$1:$V$10,Data1!$V$11:$V$123</definedName>
-    <definedName name="A2603611V_Data">Data1!$V$11:$V$123</definedName>
-    <definedName name="A2603611V_Latest">Data1!$V$123</definedName>
-    <definedName name="A2603989W">Data1!$C$1:$C$10,Data1!$C$11:$C$123</definedName>
-    <definedName name="A2603989W_Data">Data1!$C$11:$C$123</definedName>
-    <definedName name="A2603989W_Latest">Data1!$C$123</definedName>
-    <definedName name="A2603990F">Data1!$L$1:$L$10,Data1!$L$11:$L$123</definedName>
-    <definedName name="A2603990F_Data">Data1!$L$11:$L$123</definedName>
-    <definedName name="A2603990F_Latest">Data1!$L$123</definedName>
-    <definedName name="A2603991J">Data1!$U$1:$U$10,Data1!$U$11:$U$123</definedName>
-    <definedName name="A2603991J_Data">Data1!$U$11:$U$123</definedName>
-    <definedName name="A2603991J_Latest">Data1!$U$123</definedName>
-    <definedName name="A2713846W">Data1!$E$1:$E$10,Data1!$E$11:$E$123</definedName>
-    <definedName name="A2713846W_Data">Data1!$E$11:$E$123</definedName>
-    <definedName name="A2713846W_Latest">Data1!$E$123</definedName>
-    <definedName name="A2713848A">Data1!$H$1:$H$10,Data1!$H$11:$H$123</definedName>
-    <definedName name="A2713848A_Data">Data1!$H$11:$H$123</definedName>
-    <definedName name="A2713848A_Latest">Data1!$H$123</definedName>
-    <definedName name="A2713849C">Data1!$G$1:$G$10,Data1!$G$11:$G$123</definedName>
-    <definedName name="A2713849C_Data">Data1!$G$11:$G$123</definedName>
-    <definedName name="A2713849C_Latest">Data1!$G$123</definedName>
-    <definedName name="A2713851R">Data1!$J$1:$J$10,Data1!$J$11:$J$123</definedName>
-    <definedName name="A2713851R_Data">Data1!$J$11:$J$123</definedName>
-    <definedName name="A2713851R_Latest">Data1!$J$123</definedName>
-    <definedName name="A2713852T">Data1!$F$1:$F$10,Data1!$F$11:$F$123</definedName>
-    <definedName name="A2713852T_Data">Data1!$F$11:$F$123</definedName>
-    <definedName name="A2713852T_Latest">Data1!$F$123</definedName>
-    <definedName name="A2713854W">Data1!$I$1:$I$10,Data1!$I$11:$I$123</definedName>
-    <definedName name="A2713854W_Data">Data1!$I$11:$I$123</definedName>
-    <definedName name="A2713854W_Latest">Data1!$I$123</definedName>
-    <definedName name="A83895308K">Data1!$N$1:$N$10,Data1!$N$11:$N$123</definedName>
-    <definedName name="A83895308K_Data">Data1!$N$11:$N$123</definedName>
-    <definedName name="A83895308K_Latest">Data1!$N$123</definedName>
-    <definedName name="A83895309L">Data1!$W$1:$W$10,Data1!$W$11:$W$123</definedName>
-    <definedName name="A83895309L_Data">Data1!$W$11:$W$123</definedName>
-    <definedName name="A83895309L_Latest">Data1!$W$123</definedName>
-    <definedName name="A83895311X">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$123</definedName>
-    <definedName name="A83895311X_Data">Data1!$Q$11:$Q$123</definedName>
-    <definedName name="A83895311X_Latest">Data1!$Q$123</definedName>
-    <definedName name="A83895312A">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$123</definedName>
-    <definedName name="A83895312A_Data">Data1!$Z$11:$Z$123</definedName>
-    <definedName name="A83895312A_Latest">Data1!$Z$123</definedName>
-    <definedName name="A83895332K">Data1!$O$1:$O$10,Data1!$O$11:$O$123</definedName>
-    <definedName name="A83895332K_Data">Data1!$O$11:$O$123</definedName>
-    <definedName name="A83895332K_Latest">Data1!$O$123</definedName>
-    <definedName name="A83895333L">Data1!$X$1:$X$10,Data1!$X$11:$X$123</definedName>
-    <definedName name="A83895333L_Data">Data1!$X$11:$X$123</definedName>
-    <definedName name="A83895333L_Latest">Data1!$X$123</definedName>
-    <definedName name="A83895335T">Data1!$R$1:$R$10,Data1!$R$11:$R$123</definedName>
-    <definedName name="A83895335T_Data">Data1!$R$11:$R$123</definedName>
-    <definedName name="A83895335T_Latest">Data1!$R$123</definedName>
-    <definedName name="A83895336V">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$123</definedName>
-    <definedName name="A83895336V_Data">Data1!$AA$11:$AA$123</definedName>
-    <definedName name="A83895336V_Latest">Data1!$AA$123</definedName>
-    <definedName name="A83895395V">Data1!$P$1:$P$10,Data1!$P$11:$P$123</definedName>
-    <definedName name="A83895395V_Data">Data1!$P$11:$P$123</definedName>
-    <definedName name="A83895395V_Latest">Data1!$P$123</definedName>
-    <definedName name="A83895396W">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$123</definedName>
-    <definedName name="A83895396W_Data">Data1!$Y$11:$Y$123</definedName>
-    <definedName name="A83895396W_Latest">Data1!$Y$123</definedName>
-    <definedName name="A83895398A">Data1!$S$1:$S$10,Data1!$S$11:$S$123</definedName>
-    <definedName name="A83895398A_Data">Data1!$S$11:$S$123</definedName>
-    <definedName name="A83895398A_Latest">Data1!$S$123</definedName>
-    <definedName name="A83895399C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$123</definedName>
-    <definedName name="A83895399C_Data">Data1!$AB$11:$AB$123</definedName>
-    <definedName name="A83895399C_Latest">Data1!$AB$123</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$123</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$123</definedName>
+    <definedName name="A2603039T">Data1!$B$1:$B$10,Data1!$B$11:$B$124</definedName>
+    <definedName name="A2603039T_Data">Data1!$B$11:$B$124</definedName>
+    <definedName name="A2603039T_Latest">Data1!$B$124</definedName>
+    <definedName name="A2603040A">Data1!$K$1:$K$10,Data1!$K$11:$K$124</definedName>
+    <definedName name="A2603040A_Data">Data1!$K$11:$K$124</definedName>
+    <definedName name="A2603040A_Latest">Data1!$K$124</definedName>
+    <definedName name="A2603041C">Data1!$T$1:$T$10,Data1!$T$11:$T$124</definedName>
+    <definedName name="A2603041C_Data">Data1!$T$11:$T$124</definedName>
+    <definedName name="A2603041C_Latest">Data1!$T$124</definedName>
+    <definedName name="A2603609J">Data1!$D$1:$D$10,Data1!$D$11:$D$124</definedName>
+    <definedName name="A2603609J_Data">Data1!$D$11:$D$124</definedName>
+    <definedName name="A2603609J_Latest">Data1!$D$124</definedName>
+    <definedName name="A2603610T">Data1!$M$1:$M$10,Data1!$M$11:$M$124</definedName>
+    <definedName name="A2603610T_Data">Data1!$M$11:$M$124</definedName>
+    <definedName name="A2603610T_Latest">Data1!$M$124</definedName>
+    <definedName name="A2603611V">Data1!$V$1:$V$10,Data1!$V$11:$V$124</definedName>
+    <definedName name="A2603611V_Data">Data1!$V$11:$V$124</definedName>
+    <definedName name="A2603611V_Latest">Data1!$V$124</definedName>
+    <definedName name="A2603989W">Data1!$C$1:$C$10,Data1!$C$11:$C$124</definedName>
+    <definedName name="A2603989W_Data">Data1!$C$11:$C$124</definedName>
+    <definedName name="A2603989W_Latest">Data1!$C$124</definedName>
+    <definedName name="A2603990F">Data1!$L$1:$L$10,Data1!$L$11:$L$124</definedName>
+    <definedName name="A2603990F_Data">Data1!$L$11:$L$124</definedName>
+    <definedName name="A2603990F_Latest">Data1!$L$124</definedName>
+    <definedName name="A2603991J">Data1!$U$1:$U$10,Data1!$U$11:$U$124</definedName>
+    <definedName name="A2603991J_Data">Data1!$U$11:$U$124</definedName>
+    <definedName name="A2603991J_Latest">Data1!$U$124</definedName>
+    <definedName name="A2713846W">Data1!$E$1:$E$10,Data1!$E$11:$E$124</definedName>
+    <definedName name="A2713846W_Data">Data1!$E$11:$E$124</definedName>
+    <definedName name="A2713846W_Latest">Data1!$E$124</definedName>
+    <definedName name="A2713848A">Data1!$H$1:$H$10,Data1!$H$11:$H$124</definedName>
+    <definedName name="A2713848A_Data">Data1!$H$11:$H$124</definedName>
+    <definedName name="A2713848A_Latest">Data1!$H$124</definedName>
+    <definedName name="A2713849C">Data1!$G$1:$G$10,Data1!$G$11:$G$124</definedName>
+    <definedName name="A2713849C_Data">Data1!$G$11:$G$124</definedName>
+    <definedName name="A2713849C_Latest">Data1!$G$124</definedName>
+    <definedName name="A2713851R">Data1!$J$1:$J$10,Data1!$J$11:$J$124</definedName>
+    <definedName name="A2713851R_Data">Data1!$J$11:$J$124</definedName>
+    <definedName name="A2713851R_Latest">Data1!$J$124</definedName>
+    <definedName name="A2713852T">Data1!$F$1:$F$10,Data1!$F$11:$F$124</definedName>
+    <definedName name="A2713852T_Data">Data1!$F$11:$F$124</definedName>
+    <definedName name="A2713852T_Latest">Data1!$F$124</definedName>
+    <definedName name="A2713854W">Data1!$I$1:$I$10,Data1!$I$11:$I$124</definedName>
+    <definedName name="A2713854W_Data">Data1!$I$11:$I$124</definedName>
+    <definedName name="A2713854W_Latest">Data1!$I$124</definedName>
+    <definedName name="A83895308K">Data1!$N$1:$N$10,Data1!$N$11:$N$124</definedName>
+    <definedName name="A83895308K_Data">Data1!$N$11:$N$124</definedName>
+    <definedName name="A83895308K_Latest">Data1!$N$124</definedName>
+    <definedName name="A83895309L">Data1!$W$1:$W$10,Data1!$W$11:$W$124</definedName>
+    <definedName name="A83895309L_Data">Data1!$W$11:$W$124</definedName>
+    <definedName name="A83895309L_Latest">Data1!$W$124</definedName>
+    <definedName name="A83895311X">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$124</definedName>
+    <definedName name="A83895311X_Data">Data1!$Q$11:$Q$124</definedName>
+    <definedName name="A83895311X_Latest">Data1!$Q$124</definedName>
+    <definedName name="A83895312A">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$124</definedName>
+    <definedName name="A83895312A_Data">Data1!$Z$11:$Z$124</definedName>
+    <definedName name="A83895312A_Latest">Data1!$Z$124</definedName>
+    <definedName name="A83895332K">Data1!$O$1:$O$10,Data1!$O$11:$O$124</definedName>
+    <definedName name="A83895332K_Data">Data1!$O$11:$O$124</definedName>
+    <definedName name="A83895332K_Latest">Data1!$O$124</definedName>
+    <definedName name="A83895333L">Data1!$X$1:$X$10,Data1!$X$11:$X$124</definedName>
+    <definedName name="A83895333L_Data">Data1!$X$11:$X$124</definedName>
+    <definedName name="A83895333L_Latest">Data1!$X$124</definedName>
+    <definedName name="A83895335T">Data1!$R$1:$R$10,Data1!$R$11:$R$124</definedName>
+    <definedName name="A83895335T_Data">Data1!$R$11:$R$124</definedName>
+    <definedName name="A83895335T_Latest">Data1!$R$124</definedName>
+    <definedName name="A83895336V">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$124</definedName>
+    <definedName name="A83895336V_Data">Data1!$AA$11:$AA$124</definedName>
+    <definedName name="A83895336V_Latest">Data1!$AA$124</definedName>
+    <definedName name="A83895395V">Data1!$P$1:$P$10,Data1!$P$11:$P$124</definedName>
+    <definedName name="A83895395V_Data">Data1!$P$11:$P$124</definedName>
+    <definedName name="A83895395V_Latest">Data1!$P$124</definedName>
+    <definedName name="A83895396W">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$124</definedName>
+    <definedName name="A83895396W_Data">Data1!$Y$11:$Y$124</definedName>
+    <definedName name="A83895396W_Latest">Data1!$Y$124</definedName>
+    <definedName name="A83895398A">Data1!$S$1:$S$10,Data1!$S$11:$S$124</definedName>
+    <definedName name="A83895398A_Data">Data1!$S$11:$S$124</definedName>
+    <definedName name="A83895398A_Latest">Data1!$S$124</definedName>
+    <definedName name="A83895399C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$124</definedName>
+    <definedName name="A83895399C_Data">Data1!$AB$11:$AB$124</definedName>
+    <definedName name="A83895399C_Latest">Data1!$AB$124</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$124</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$124</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1184,7 +1184,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2025</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -1865,10 +1865,10 @@
         <v>35674</v>
       </c>
       <c r="G12" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H12" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>24</v>
@@ -1897,10 +1897,10 @@
         <v>35674</v>
       </c>
       <c r="G13" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H13" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>24</v>
@@ -1929,10 +1929,10 @@
         <v>35674</v>
       </c>
       <c r="G14" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H14" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>24</v>
@@ -1961,10 +1961,10 @@
         <v>35674</v>
       </c>
       <c r="G15" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H15" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>24</v>
@@ -1993,10 +1993,10 @@
         <v>35674</v>
       </c>
       <c r="G16" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H16" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>24</v>
@@ -2025,10 +2025,10 @@
         <v>35674</v>
       </c>
       <c r="G17" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H17" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>24</v>
@@ -2057,10 +2057,10 @@
         <v>35674</v>
       </c>
       <c r="G18" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H18" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>24</v>
@@ -2089,10 +2089,10 @@
         <v>35674</v>
       </c>
       <c r="G19" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H19" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>24</v>
@@ -2121,10 +2121,10 @@
         <v>35674</v>
       </c>
       <c r="G20" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H20" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>24</v>
@@ -2153,10 +2153,10 @@
         <v>35674</v>
       </c>
       <c r="G21" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H21" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>39</v>
@@ -2185,10 +2185,10 @@
         <v>35674</v>
       </c>
       <c r="G22" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H22" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>39</v>
@@ -2217,10 +2217,10 @@
         <v>35674</v>
       </c>
       <c r="G23" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H23" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>39</v>
@@ -2249,10 +2249,10 @@
         <v>35674</v>
       </c>
       <c r="G24" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H24" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>39</v>
@@ -2281,10 +2281,10 @@
         <v>35674</v>
       </c>
       <c r="G25" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H25" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>39</v>
@@ -2313,10 +2313,10 @@
         <v>35674</v>
       </c>
       <c r="G26" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H26" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>39</v>
@@ -2345,10 +2345,10 @@
         <v>35674</v>
       </c>
       <c r="G27" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H27" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>39</v>
@@ -2377,10 +2377,10 @@
         <v>35674</v>
       </c>
       <c r="G28" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H28" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>39</v>
@@ -2409,10 +2409,10 @@
         <v>35674</v>
       </c>
       <c r="G29" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H29" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>39</v>
@@ -2441,10 +2441,10 @@
         <v>35674</v>
       </c>
       <c r="G30" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H30" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>39</v>
@@ -2473,10 +2473,10 @@
         <v>35674</v>
       </c>
       <c r="G31" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H31" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>39</v>
@@ -2505,10 +2505,10 @@
         <v>35674</v>
       </c>
       <c r="G32" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H32" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>39</v>
@@ -2537,10 +2537,10 @@
         <v>35674</v>
       </c>
       <c r="G33" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H33" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>39</v>
@@ -2569,10 +2569,10 @@
         <v>35674</v>
       </c>
       <c r="G34" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H34" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>39</v>
@@ -2601,10 +2601,10 @@
         <v>35674</v>
       </c>
       <c r="G35" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H35" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>39</v>
@@ -2633,10 +2633,10 @@
         <v>35674</v>
       </c>
       <c r="G36" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H36" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>39</v>
@@ -2665,10 +2665,10 @@
         <v>35674</v>
       </c>
       <c r="G37" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H37" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>39</v>
@@ -2697,10 +2697,10 @@
         <v>35674</v>
       </c>
       <c r="G38" s="9">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H38" s="10">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>39</v>
@@ -2762,7 +2762,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB123"/>
+  <dimension ref="A1:AB124"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -3372,85 +3372,85 @@
         <v>21</v>
       </c>
       <c r="B8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="C8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="D8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="E8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="F8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="G8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="H8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="I8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="J8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="K8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="L8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="M8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="N8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="O8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="P8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="Q8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="R8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="S8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="T8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="U8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="V8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="W8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="X8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="Y8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="Z8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="AA8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="AB8" s="6">
-        <v>45901</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -3458,85 +3458,85 @@
         <v>22</v>
       </c>
       <c r="B9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="V9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="X9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB9" s="1">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -6393,7 +6393,7 @@
         <v>87.9</v>
       </c>
       <c r="G44" s="8">
-        <v>88.3</v>
+        <v>88.2</v>
       </c>
       <c r="H44" s="8">
         <v>88.4</v>
@@ -6420,7 +6420,7 @@
         <v>0.9</v>
       </c>
       <c r="P44" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q44" s="8">
         <v>1</v>
@@ -6447,7 +6447,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="Y44" s="8">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="Z44" s="8">
         <v>4</v>
@@ -6506,7 +6506,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="P45" s="8">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Q45" s="8">
         <v>1</v>
@@ -6791,7 +6791,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="Y48" s="8">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="Z48" s="8">
         <v>4</v>
@@ -12410,7 +12410,7 @@
         <v>145</v>
       </c>
       <c r="F114" s="8">
-        <v>147.69999999999999</v>
+        <v>147.6</v>
       </c>
       <c r="G114" s="8">
         <v>145.6</v>
@@ -12493,16 +12493,16 @@
         <v>147.9</v>
       </c>
       <c r="E115" s="8">
-        <v>147</v>
+        <v>147.1</v>
       </c>
       <c r="F115" s="8">
-        <v>149.1</v>
+        <v>149.19999999999999</v>
       </c>
       <c r="G115" s="8">
         <v>147.5</v>
       </c>
       <c r="H115" s="8">
-        <v>146.80000000000001</v>
+        <v>146.9</v>
       </c>
       <c r="I115" s="8">
         <v>149.4</v>
@@ -12523,13 +12523,13 @@
         <v>1.4</v>
       </c>
       <c r="O115" s="8">
-        <v>0.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P115" s="8">
         <v>1.3</v>
       </c>
       <c r="Q115" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="R115" s="8">
         <v>1.1000000000000001</v>
@@ -12547,7 +12547,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="W115" s="8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X115" s="8">
         <v>3.5</v>
@@ -12556,7 +12556,7 @@
         <v>4</v>
       </c>
       <c r="Z115" s="8">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="AA115" s="8">
         <v>3.7</v>
@@ -12606,7 +12606,7 @@
         <v>0.9</v>
       </c>
       <c r="N116" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O116" s="8">
         <v>1.5</v>
@@ -12615,7 +12615,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="Q116" s="8">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="R116" s="8">
         <v>1</v>
@@ -12808,7 +12808,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="X118" s="8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y118" s="8">
         <v>4.0999999999999996</v>
@@ -12843,13 +12843,13 @@
         <v>154.6</v>
       </c>
       <c r="G119" s="8">
-        <v>152.69999999999999</v>
+        <v>152.80000000000001</v>
       </c>
       <c r="H119" s="8">
-        <v>152.1</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="I119" s="8">
-        <v>154.5</v>
+        <v>154.6</v>
       </c>
       <c r="J119" s="8">
         <v>152.69999999999999</v>
@@ -12870,13 +12870,13 @@
         <v>0.7</v>
       </c>
       <c r="P119" s="8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q119" s="8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="R119" s="8">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="S119" s="8">
         <v>0.8</v>
@@ -12894,16 +12894,16 @@
         <v>3.5</v>
       </c>
       <c r="X119" s="8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y119" s="8">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z119" s="8">
         <v>3.6</v>
       </c>
       <c r="AA119" s="8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB119" s="8">
         <v>3.6</v>
@@ -12956,13 +12956,13 @@
         <v>0.7</v>
       </c>
       <c r="P120" s="8">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q120" s="8">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R120" s="8">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S120" s="8">
         <v>0.9</v>
@@ -13015,7 +13015,7 @@
         <v>157.5</v>
       </c>
       <c r="G121" s="8">
-        <v>155.4</v>
+        <v>155.30000000000001</v>
       </c>
       <c r="H121" s="8">
         <v>154.69999999999999</v>
@@ -13042,7 +13042,7 @@
         <v>1.2</v>
       </c>
       <c r="P121" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q121" s="8">
         <v>0.8</v>
@@ -13069,7 +13069,7 @@
         <v>3.6</v>
       </c>
       <c r="Y121" s="8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z121" s="8">
         <v>3.3</v>
@@ -13128,7 +13128,7 @@
         <v>1</v>
       </c>
       <c r="P122" s="8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Q122" s="8">
         <v>0.8</v>
@@ -13181,10 +13181,10 @@
         <v>158.30000000000001</v>
       </c>
       <c r="E123" s="8">
-        <v>157.1</v>
+        <v>157.19999999999999</v>
       </c>
       <c r="F123" s="8">
-        <v>160.5</v>
+        <v>160.6</v>
       </c>
       <c r="G123" s="8">
         <v>157.9</v>
@@ -13193,10 +13193,10 @@
         <v>157.19999999999999</v>
       </c>
       <c r="I123" s="8">
-        <v>160.6</v>
+        <v>160.5</v>
       </c>
       <c r="J123" s="8">
-        <v>157.9</v>
+        <v>158</v>
       </c>
       <c r="K123" s="8">
         <v>1.4</v>
@@ -13208,7 +13208,7 @@
         <v>1.3</v>
       </c>
       <c r="N123" s="8">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O123" s="8">
         <v>0.9</v>
@@ -13220,10 +13220,10 @@
         <v>0.8</v>
       </c>
       <c r="R123" s="8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S123" s="8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T123" s="8">
         <v>3.3</v>
@@ -13235,21 +13235,107 @@
         <v>3.4</v>
       </c>
       <c r="W123" s="8">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="X123" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="Y123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="Z123" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="AA123" s="8">
         <v>3.8</v>
       </c>
-      <c r="Y123" s="8">
+      <c r="AB123" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A124" s="9">
+        <v>45992</v>
+      </c>
+      <c r="B124" s="8">
+        <v>158.69999999999999</v>
+      </c>
+      <c r="C124" s="8">
+        <v>161.9</v>
+      </c>
+      <c r="D124" s="8">
+        <v>159.4</v>
+      </c>
+      <c r="E124" s="8">
+        <v>158.5</v>
+      </c>
+      <c r="F124" s="8">
+        <v>161.9</v>
+      </c>
+      <c r="G124" s="8">
+        <v>159.19999999999999</v>
+      </c>
+      <c r="H124" s="8">
+        <v>158.4</v>
+      </c>
+      <c r="I124" s="8">
+        <v>162</v>
+      </c>
+      <c r="J124" s="8">
+        <v>159.19999999999999</v>
+      </c>
+      <c r="K124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="L124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="M124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="N124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="O124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="P124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="Q124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="R124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="S124" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="T124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="U124" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="V124" s="8">
         <v>3.4</v>
       </c>
-      <c r="Z123" s="8">
+      <c r="W124" s="8">
         <v>3.4</v>
       </c>
-      <c r="AA123" s="8">
+      <c r="X124" s="8">
+        <v>4</v>
+      </c>
+      <c r="Y124" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="Z124" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="AA124" s="8">
         <v>3.9</v>
       </c>
-      <c r="AB123" s="8">
+      <c r="AB124" s="8">
         <v>3.4</v>
       </c>
     </row>
